--- a/config/rules/.history/PDS002MI.xlsx
+++ b/config/rules/.history/PDS002MI.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rules" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet name="_Audit_Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -78,13 +78,13 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -2943,11 +2943,7 @@
           <t>MSEQ</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>MSEQ</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>DIRECT</t>
@@ -3831,15 +3827,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PLGR</t>
+          <t>FACI,PLGR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>MAP</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>translation_tbl\PDS002-PLGR.xlsx|FACILITY|OLD|NEW</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>GLOBAL</t>
@@ -5756,27 +5756,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Detailed Backflush</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Detailed Backflush</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5893,27 +5893,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Attribute Number</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Attribute Number</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6709,27 +6709,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>External Line Reference</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>External Line Reference</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7351,27 +7351,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Inherit substitution table</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Inherit substitution table</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7398,27 +7398,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Intermediate Stock</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Intermediate Stock</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7659,27 +7659,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Main material line</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Main material line</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7794,27 +7794,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Component Price</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Component Price</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -9184,27 +9184,27 @@
           <t>GLOBAL</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Shipping buffer in production days</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Shipping buffer in production days</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10219,7 +10219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12301,6 +12301,114 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:03:57</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>FDAT</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Val: '20251101.0'-&gt;'20251101'</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:03:57</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MSEQ</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: MSEQ-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-30 14:03:57</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>PLGR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;MAP, Src: PLGR-&gt;FACI,PLGR, Val: ''-&gt;'translation_tbl\PDS002-PLGR.xlsx|FACILITY|OLD|NEW'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-02 15:01:19</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MSEQ</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Type: IGNORE-&gt;DIRECT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
